--- a/sheets/민요/검수/남원산성.xlsx
+++ b/sheets/민요/검수/남원산성.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,57 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2511,8 +2642,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2527,748 +2662,639 @@
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">남원산성 — 민요채보-1/남원산성.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">남원산성</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">꾀</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="16"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="20"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">꼬</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">양</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">진</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">원</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="16"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="22"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="16"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="20"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">능</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">싸</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="16"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="22"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="J11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">올</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="L11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="16"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="20"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">계</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">청</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="J13" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="16"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="22"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">짹</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K15" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="L15" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M15" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="16"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="20"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">浦</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">끼</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="L17" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="M17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="16"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="22"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:M2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/남원산성.xlsx
+++ b/sheets/민요/검수/남원산성.xlsx
@@ -259,11 +259,7 @@
           <t xml:space="preserve">쪽</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196</t>
-        </is>
-      </c>
+      <c r="B5" s="4"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -4251,10 +4247,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s=""/>
-      <c r="B1" s="">
-        <v>0</v>
-      </c>
+      <c r="A1" s="0"/>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>

--- a/sheets/민요/검수/남원산성.xlsx
+++ b/sheets/민요/검수/남원산성.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -553,13 +553,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="2"/>
@@ -747,12 +747,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="2"/>
@@ -782,13 +782,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -857,13 +857,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -976,12 +976,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="2"/>
@@ -1011,13 +1011,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1090,13 +1090,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I17" s="2"/>
@@ -1165,13 +1165,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―</t>
+          <t xml:space="preserve">–|–</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -1394,13 +1394,13 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1718,13 +1718,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1833,12 +1833,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I35" s="2"/>
@@ -1868,13 +1868,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -1947,13 +1947,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2105,13 +2105,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2184,13 +2184,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―南</t>
+          <t xml:space="preserve">潢|–南</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I47" s="2"/>
@@ -2338,13 +2338,13 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2729,13 +2729,13 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―㴌</t>
+          <t xml:space="preserve">–㴌</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―㴌</t>
+          <t xml:space="preserve">–㴌</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3319,13 +3319,13 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―姑</t>
+          <t xml:space="preserve">潢|–姑</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑</t>
+          <t xml:space="preserve">–姑</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑</t>
+          <t xml:space="preserve">–姑</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑</t>
+          <t xml:space="preserve">–姑</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑</t>
+          <t xml:space="preserve">–姑</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I82" s="2"/>
@@ -3750,12 +3750,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑</t>
+          <t xml:space="preserve">–姑</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑</t>
+          <t xml:space="preserve">–姑</t>
         </is>
       </c>
       <c r="I84" s="2"/>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I86" s="2"/>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -4167,13 +4167,13 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳|―無</t>
+          <t xml:space="preserve">湳|–無</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -4316,8 +4316,8 @@
       </c>
       <c r="J3" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="K3" s="8" t="inlineStr">
@@ -4328,7 +4328,7 @@
       <c r="L3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr">
@@ -4341,7 +4341,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C4" s="9"/>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="9"/>
@@ -4430,7 +4430,7 @@
       <c r="H5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4465,7 +4465,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑</t>
+          <t xml:space="preserve">–姑</t>
         </is>
       </c>
       <c r="C6" s="10"/>
@@ -4499,7 +4499,7 @@
       <c r="K6" s="10"/>
       <c r="L6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M6" s="10"/>
@@ -4542,7 +4542,7 @@
       <c r="H7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -4577,7 +4577,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C8" s="9"/>
@@ -4619,7 +4619,7 @@
       <c r="K8" s="9"/>
       <c r="L8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M8" s="9"/>
@@ -4672,7 +4672,7 @@
       <c r="J9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr">
@@ -4683,7 +4683,7 @@
       <c r="L9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
@@ -4702,7 +4702,7 @@
       <c r="C10" s="10"/>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4752,7 +4752,7 @@
       <c r="D11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -4763,7 +4763,7 @@
       <c r="F11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -4774,7 +4774,7 @@
       <c r="H11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
@@ -4796,7 +4796,7 @@
       <c r="L11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -4906,7 +4906,7 @@
       <c r="H13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -4947,7 +4947,7 @@
       <c r="C14" s="10"/>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑</t>
+          <t xml:space="preserve">–姑</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="J14" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="L14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M14" s="10"/>
@@ -5052,7 +5052,7 @@
       <c r="L15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
@@ -5065,7 +5065,7 @@
       <c r="A16" s="0"/>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑</t>
+          <t xml:space="preserve">–姑</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="F16" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―㴌</t>
+          <t xml:space="preserve">–㴌</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -5095,13 +5095,13 @@
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
@@ -5125,7 +5125,7 @@
       <c r="B17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -5158,7 +5158,7 @@
       <c r="H17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
@@ -5169,7 +5169,7 @@
       <c r="J17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
@@ -5180,7 +5180,7 @@
       <c r="L17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="M17" s="9" t="inlineStr">
@@ -5227,7 +5227,7 @@
       <c r="K18" s="10"/>
       <c r="L18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M18" s="10"/>

--- a/sheets/민요/검수/남원산성.xlsx
+++ b/sheets/민요/검수/남원산성.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4251,87 +4292,87 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">남원산성</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꾀꼬</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">석양</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">수진</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">남원</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4339,54 +4380,54 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="23"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="I4" s="23"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4394,68 +4435,68 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">리는</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
 潢</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">늘어져</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">날진</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">허어</t>
         </is>
@@ -4463,111 +4504,111 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–姑</t>
         </is>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="C6" s="24"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="K6" s="24"/>
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M6" s="10"/>
+      <c r="M6" s="24"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">짝을</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">갈매</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">해동</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">올</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어허</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="M7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어허</t>
         </is>
@@ -4575,118 +4616,118 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="23"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">청</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="23"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M8" s="9"/>
+      <c r="M8" s="23"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南㴌</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">지어</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">울고</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南南
 南</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">보라매</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無^
 ﾉ</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -4694,112 +4735,112 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="24"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="24"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="24"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="24"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K10" s="10" t="inlineStr">
+      <c r="K10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M10" s="10"/>
+      <c r="M10" s="24"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이산으</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –姑</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">능수</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">떴</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">둥가</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="M11" s="8" t="inlineStr">
+      <c r="M11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4807,62 +4848,62 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南南</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">버</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr">
+      <c r="M12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4870,68 +4911,68 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">가면</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△㴌
 潢</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">들가</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南姑</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">보아</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –南</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">문</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△㴌
 潢</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">사랑</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아하</t>
         </is>
@@ -4939,123 +4980,123 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="24"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–姑</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
       </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="J14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="K14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
+      <c r="M14" s="24"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꾀꼬</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">휘늘</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">저종</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南南
 南</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">바라보</t>
         </is>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="J15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr">
+      <c r="K15" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
@@ -5063,58 +5104,58 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–姑</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–㴌</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">옹</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="I16" s="23"/>
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="L16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢姑</t>
         </is>
       </c>
-      <c r="M16" s="9" t="inlineStr">
+      <c r="M16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5122,68 +5163,68 @@
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 –無</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">루리</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">진데</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">달새</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="M17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5191,46 +5232,46 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="24"/>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="24"/>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="I18" s="24"/>
+      <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="K18" s="24"/>
+      <c r="L18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M18" s="10"/>
+      <c r="M18" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/남원산성.xlsx
+++ b/sheets/민요/검수/남원산성.xlsx
@@ -4273,24 +4273,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="60.41" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="60.41" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="60.41" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="60.41" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="60.41" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="M6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="60.41" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="60.41" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="60.41" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="60.41" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="M10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="60.41" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="60.41" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="60.41" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4978,11 +4978,11 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="60.41" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C14" s="24"/>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="M14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="60.41" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="60.41" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="60.41" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="60.41" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/남원산성.xlsx
+++ b/sheets/민요/검수/남원산성.xlsx
@@ -4319,7 +4319,8 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">꾀꼬</t>
+          <t xml:space="preserve">꾀
+꼬</t>
         </is>
       </c>
       <c r="D3" s="21" t="inlineStr">
@@ -4330,7 +4331,8 @@
       </c>
       <c r="E3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">석양</t>
+          <t xml:space="preserve">석
+양</t>
         </is>
       </c>
       <c r="F3" s="21" t="inlineStr">
@@ -4341,7 +4343,8 @@
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">수진</t>
+          <t xml:space="preserve">수
+진</t>
         </is>
       </c>
       <c r="H3" s="21" t="inlineStr">
@@ -4352,7 +4355,8 @@
       </c>
       <c r="I3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">남원</t>
+          <t xml:space="preserve">남
+원</t>
         </is>
       </c>
       <c r="J3" s="21" t="inlineStr">
@@ -4443,7 +4447,8 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">리는</t>
+          <t xml:space="preserve">리
+는</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -4454,7 +4459,9 @@
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">늘어져</t>
+          <t xml:space="preserve">늘
+어
+져</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -4465,7 +4472,8 @@
       </c>
       <c r="G5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">날진</t>
+          <t xml:space="preserve">날
+진</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -4498,7 +4506,8 @@
       </c>
       <c r="M5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">허어</t>
+          <t xml:space="preserve">허
+어</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4564,8 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">짝을</t>
+          <t xml:space="preserve">짝
+을</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -4566,7 +4576,8 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">갈매</t>
+          <t xml:space="preserve">갈
+매</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -4577,7 +4588,8 @@
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">해동</t>
+          <t xml:space="preserve">해
+동</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -4599,7 +4611,8 @@
       </c>
       <c r="K7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">어허</t>
+          <t xml:space="preserve">어
+허</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -4610,7 +4623,8 @@
       </c>
       <c r="M7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">어허</t>
+          <t xml:space="preserve">어
+허</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4688,8 @@
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">지어</t>
+          <t xml:space="preserve">지
+어</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -4685,7 +4700,8 @@
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">울고</t>
+          <t xml:space="preserve">울
+고</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -4696,7 +4712,9 @@
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">보라매</t>
+          <t xml:space="preserve">보
+라
+매</t>
         </is>
       </c>
       <c r="H9" s="25" t="inlineStr">
@@ -4787,7 +4805,9 @@
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">이산으</t>
+          <t xml:space="preserve">이
+산
+으</t>
         </is>
       </c>
       <c r="D11" s="25" t="inlineStr">
@@ -4798,7 +4818,8 @@
       </c>
       <c r="E11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">능수</t>
+          <t xml:space="preserve">능
+수</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -4831,7 +4852,8 @@
       </c>
       <c r="K11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">둥가</t>
+          <t xml:space="preserve">둥
+가</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -4919,7 +4941,8 @@
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">가면</t>
+          <t xml:space="preserve">가
+면</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -4930,7 +4953,8 @@
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">들가</t>
+          <t xml:space="preserve">들
+가</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -4941,7 +4965,8 @@
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">보아</t>
+          <t xml:space="preserve">보
+아</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -4963,7 +4988,8 @@
       </c>
       <c r="K13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">사랑</t>
+          <t xml:space="preserve">사
+랑</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -4974,7 +5000,8 @@
       </c>
       <c r="M13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">아하</t>
+          <t xml:space="preserve">아
+하</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5070,8 @@
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">꾀꼬</t>
+          <t xml:space="preserve">꾀
+꼬</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -5054,7 +5082,8 @@
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">휘늘</t>
+          <t xml:space="preserve">휘
+늘</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -5065,7 +5094,8 @@
       </c>
       <c r="G15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">저종</t>
+          <t xml:space="preserve">저
+종</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -5076,7 +5106,9 @@
       </c>
       <c r="I15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">바라보</t>
+          <t xml:space="preserve">바
+라
+보</t>
         </is>
       </c>
       <c r="J15" s="25" t="inlineStr">
@@ -5171,7 +5203,8 @@
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">루리</t>
+          <t xml:space="preserve">루
+리</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -5182,7 +5215,8 @@
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">진데</t>
+          <t xml:space="preserve">진
+데</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -5193,7 +5227,8 @@
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">달새</t>
+          <t xml:space="preserve">달
+새</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">

--- a/sheets/민요/검수/남원산성.xlsx
+++ b/sheets/민요/검수/남원산성.xlsx
@@ -548,7 +548,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -559,7 +558,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -573,7 +571,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -584,7 +581,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -604,7 +600,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -615,7 +610,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -629,7 +623,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -640,7 +633,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -654,7 +646,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -665,7 +656,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -675,7 +665,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -685,7 +674,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -695,7 +683,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -706,7 +693,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -720,7 +706,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -731,7 +716,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -751,7 +735,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -762,7 +745,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -776,7 +758,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -787,7 +768,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -797,7 +777,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -808,7 +787,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -836,7 +814,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -846,7 +823,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -861,7 +837,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -872,7 +847,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -891,7 +865,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -899,7 +872,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -909,7 +881,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -924,7 +895,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -935,7 +905,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -949,7 +918,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -958,7 +926,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -975,7 +942,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -985,7 +951,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -996,7 +961,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1006,7 +970,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1021,7 +984,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1032,7 +994,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1042,7 +1003,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1053,7 +1013,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1069,7 +1028,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1079,7 +1037,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1095,7 +1052,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1105,7 +1061,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1124,7 +1079,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1135,7 +1089,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1150,7 +1103,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1160,7 +1112,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1175,7 +1126,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1183,7 +1133,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1193,7 +1142,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1209,7 +1157,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1219,7 +1166,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1235,7 +1181,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1245,7 +1190,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1254,7 +1198,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1269,7 +1212,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1279,7 +1221,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1295,7 +1236,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1306,7 +1246,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1320,7 +1259,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1330,7 +1268,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1356,7 +1293,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1366,7 +1302,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1382,7 +1317,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -1391,7 +1325,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1408,7 +1341,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1418,7 +1350,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1433,7 +1364,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1443,7 +1373,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1451,7 +1380,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1466,7 +1394,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1476,7 +1403,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1485,7 +1411,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1501,7 +1426,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1511,7 +1435,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1530,7 +1453,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1539,7 +1461,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1549,7 +1470,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1559,7 +1479,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1570,7 +1489,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1580,7 +1498,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1590,7 +1507,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1606,7 +1522,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -1615,17 +1531,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -1668,6 +1584,18 @@
       <sz val="24"/>
       <name val="궁서체"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="궁서체"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1761,7 +1689,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1815,6 +1743,46 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5200,337 +5168,337 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="15" width="6"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="29.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="18" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="19" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="M5" s="19" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="21" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="18" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="23" t="s">
         <v>219</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="M8" s="19" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="K9" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="M9" s="19" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="21" t="s">
         <v>49</v>
       </c>
     </row>

--- a/sheets/민요/검수/남원산성.xlsx
+++ b/sheets/민요/검수/남원산성.xlsx
@@ -1613,10 +1613,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/남원산성.xlsx
+++ b/sheets/민요/검수/남원산성.xlsx
@@ -546,46 +546,18 @@
     <t xml:space="preserve">루</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
+    <t xml:space="preserve">南
 南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+–</t>
   </si>
   <si>
     <t xml:space="preserve">꾀
 꼬</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
+    <t xml:space="preserve">潢
 潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+潢</t>
   </si>
   <si>
     <t xml:space="preserve">석
@@ -598,129 +570,45 @@
 이</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑
+    <t xml:space="preserve">姑
 姑
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+–</t>
   </si>
   <si>
     <t xml:space="preserve">남
 원</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
+    <t xml:space="preserve">–
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+潢</t>
   </si>
   <si>
     <t xml:space="preserve">어
 둥</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
+    <t xml:space="preserve">南
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">姑</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">어
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">어</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
+姑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어
+어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南
 南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–姑</t>
-    </r>
+–姑</t>
   </si>
   <si>
     <t xml:space="preserve">리
 는</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢潢
+    <t xml:space="preserve">潢潢
 潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ﾉ</t>
-    </r>
+ﾉ</t>
   </si>
   <si>
     <t xml:space="preserve">늘
@@ -733,65 +621,23 @@
 이</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
+    <t xml:space="preserve">南
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+潢</t>
   </si>
   <si>
     <t xml:space="preserve">산
 성</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
+    <t xml:space="preserve">–
 無
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑
+△</t>
+  </si>
+  <si>
+    <t xml:space="preserve">姑
 潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+–</t>
   </si>
   <si>
     <t xml:space="preserve">허
@@ -812,46 +658,18 @@
 찬</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
+    <t xml:space="preserve">南
+–
 㴌</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">올
 라</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
+    <t xml:space="preserve">南
 南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
+△</t>
   </si>
   <si>
     <t xml:space="preserve">어
@@ -863,76 +681,27 @@
 –</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢
+    <t xml:space="preserve">南㴌
+潢
 ﾉ</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">지
 어</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
+    <t xml:space="preserve">潢
 南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
+△</t>
   </si>
   <si>
     <t xml:space="preserve">울
 고</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
+    <t xml:space="preserve">南南
 南
 △</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">보
@@ -940,84 +709,28 @@
 매</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無^
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ﾉ
+    <t xml:space="preserve">無^
+ﾉ
 △</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
+  </si>
+  <si>
+    <t xml:space="preserve">南
+–
 姑</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">둥
 가</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑
+    <t xml:space="preserve">姑
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
+△</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南
 南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南南</t>
-    </r>
+南南</t>
   </si>
   <si>
     <t xml:space="preserve">이
@@ -1026,23 +739,9 @@
 포</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–姑
+    <t xml:space="preserve">潢
+–姑
 南</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">능
@@ -1050,23 +749,9 @@
 버</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ﾉ
+    <t xml:space="preserve">潢
+ﾉ
 南</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">떳
@@ -1077,23 +762,9 @@
 화</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
+    <t xml:space="preserve">南
 南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+南</t>
   </si>
   <si>
     <t xml:space="preserve">둥
@@ -1101,53 +772,18 @@
 내</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
+    <t xml:space="preserve">南
+南
 –</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">가
 면</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢
+    <t xml:space="preserve">△㴌
+潢
 –㴌</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">들
@@ -1155,23 +791,9 @@
 지</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南姑
+    <t xml:space="preserve">潢
+南姑
 –南</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">보
@@ -1179,54 +801,18 @@
 라</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+    <t xml:space="preserve">潢
+–南
+潢</t>
   </si>
   <si>
     <t xml:space="preserve">문
 전</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">△㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢
+    <t xml:space="preserve">△㴌
+潢
 –</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">사
@@ -1234,46 +820,18 @@
 이</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
+    <t xml:space="preserve">南
 姑
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+–</t>
   </si>
   <si>
     <t xml:space="preserve">야
 하</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
+    <t xml:space="preserve">南
+南
 –南</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">꾀
@@ -1291,23 +849,9 @@
 어</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
+    <t xml:space="preserve">潢
+南
 –㴌</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">저
@@ -1315,23 +859,9 @@
 옹</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
+    <t xml:space="preserve">南南
 南
 –</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">바
@@ -1339,84 +869,26 @@
 보</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">姑
+    <t xml:space="preserve">南
+姑
 –南</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">로
 구</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑</t>
-    </r>
+    <t xml:space="preserve">南
+潢姑</t>
   </si>
   <si>
     <t xml:space="preserve">디
 여</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">湳
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–無
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">湳</t>
-    </r>
+    <t xml:space="preserve">湳
+–無
+湳</t>
   </si>
   <si>
     <t xml:space="preserve">루
@@ -1424,23 +896,9 @@
 루</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢
+    <t xml:space="preserve">潢
 南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
+△</t>
   </si>
   <si>
     <t xml:space="preserve">진
@@ -1451,68 +909,19 @@
 새</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">姑
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
+    <t xml:space="preserve">姑
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
+△</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南
+–
+△</t>
+  </si>
+  <si>
+    <t xml:space="preserve">潢
+–
 –</t>
-    </r>
   </si>
 </sst>
 </file>
@@ -5159,7 +4568,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B2:M10"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -5179,7 +4588,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="15" width="6"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="29.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="51.95" customHeight="true">
       <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
@@ -5195,7 +4605,7 @@
       <c r="L2" s="16"/>
       <c r="M2" s="16"/>
     </row>
-    <row r="3" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
       <c r="B3" s="17" t="s">
         <v>166</v>
       </c>
@@ -5233,7 +4643,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
       <c r="B4" s="17" t="s">
         <v>177</v>
       </c>
@@ -5271,7 +4681,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
       <c r="B5" s="17" t="s">
         <v>166</v>
       </c>
@@ -5309,7 +4719,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
       <c r="B6" s="20" t="s">
         <v>195</v>
       </c>
@@ -5347,7 +4757,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
       <c r="B7" s="17" t="s">
         <v>205</v>
       </c>
@@ -5385,7 +4795,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
       <c r="B8" s="17" t="s">
         <v>214</v>
       </c>
@@ -5423,7 +4833,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
       <c r="B9" s="17" t="s">
         <v>226</v>
       </c>
@@ -5461,7 +4871,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="75.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
       <c r="B10" s="17" t="s">
         <v>238</v>
       </c>
@@ -5505,7 +4915,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="77" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/남원산성.xlsx
+++ b/sheets/민요/검수/남원산성.xlsx
@@ -4574,22 +4574,22 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="15" width="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="51.95" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.19" customHeight="true">
       <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
@@ -4605,7 +4605,7 @@
       <c r="L2" s="16"/>
       <c r="M2" s="16"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="107.43" customHeight="true">
       <c r="B3" s="17" t="s">
         <v>166</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="107.43" customHeight="true">
       <c r="B4" s="17" t="s">
         <v>177</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="107.43" customHeight="true">
       <c r="B5" s="17" t="s">
         <v>166</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="107.43" customHeight="true">
       <c r="B6" s="20" t="s">
         <v>195</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="107.43" customHeight="true">
       <c r="B7" s="17" t="s">
         <v>205</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="107.43" customHeight="true">
       <c r="B8" s="17" t="s">
         <v>214</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="107.43" customHeight="true">
       <c r="B9" s="17" t="s">
         <v>226</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="107.43" customHeight="true">
       <c r="B10" s="17" t="s">
         <v>238</v>
       </c>
@@ -4915,7 +4915,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="83"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
